--- a/sheets/S08A22P238.xlsx
+++ b/sheets/S08A22P238.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9000" uniqueCount="2117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9000" uniqueCount="2116">
   <si>
     <t>Voter ID</t>
   </si>
@@ -6254,9 +6254,6 @@
   </si>
   <si>
     <t>IOX1744739</t>
-  </si>
-  <si>
-    <t>Gharaunda,Karnal,HR</t>
   </si>
   <si>
     <t>IOX1757178</t>
@@ -35516,7 +35513,7 @@
         <v>1929</v>
       </c>
       <c r="C1107" t="s">
-        <v>2081</v>
+        <v>13</v>
       </c>
       <c r="D1107" t="s">
         <v>11</v>
@@ -35536,7 +35533,7 @@
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="B1108" t="s">
         <v>56</v>
@@ -35562,10 +35559,10 @@
     </row>
     <row r="1109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B1109" t="s">
         <v>2083</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>2084</v>
       </c>
       <c r="C1109" t="s">
         <v>124</v>
@@ -35588,10 +35585,10 @@
     </row>
     <row r="1110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B1110" t="s">
         <v>2085</v>
-      </c>
-      <c r="B1110" t="s">
-        <v>2086</v>
       </c>
       <c r="C1110" t="s">
         <v>180</v>
@@ -35614,13 +35611,13 @@
     </row>
     <row r="1111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B1111" t="s">
         <v>2087</v>
       </c>
-      <c r="B1111" t="s">
+      <c r="C1111" t="s">
         <v>2088</v>
-      </c>
-      <c r="C1111" t="s">
-        <v>2089</v>
       </c>
       <c r="D1111" t="s">
         <v>11</v>
@@ -35640,13 +35637,13 @@
     </row>
     <row r="1112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1112" t="s">
         <v>2090</v>
       </c>
-      <c r="B1112" t="s">
+      <c r="C1112" t="s">
         <v>2091</v>
-      </c>
-      <c r="C1112" t="s">
-        <v>2092</v>
       </c>
       <c r="D1112" t="s">
         <v>11</v>
@@ -35666,13 +35663,13 @@
     </row>
     <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="B1113" t="s">
         <v>1858</v>
       </c>
       <c r="C1113" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="D1113" t="s">
         <v>11</v>
@@ -35692,10 +35689,10 @@
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B1114" t="s">
         <v>2095</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>2096</v>
       </c>
       <c r="C1114" t="s">
         <v>1170</v>
@@ -35718,10 +35715,10 @@
     </row>
     <row r="1115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1115" t="s">
         <v>2097</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>2098</v>
       </c>
       <c r="C1115" t="s">
         <v>922</v>
@@ -35744,10 +35741,10 @@
     </row>
     <row r="1116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B1116" t="s">
         <v>2099</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>2100</v>
       </c>
       <c r="C1116" t="s">
         <v>442</v>
@@ -35770,7 +35767,7 @@
     </row>
     <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="B1117" t="s">
         <v>2030</v>
@@ -35796,10 +35793,10 @@
     </row>
     <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1118" t="s">
         <v>2102</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>2103</v>
       </c>
       <c r="C1118" t="s">
         <v>56</v>
@@ -35822,13 +35819,13 @@
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1119" t="s">
         <v>2104</v>
       </c>
-      <c r="B1119" t="s">
+      <c r="C1119" t="s">
         <v>2105</v>
-      </c>
-      <c r="C1119" t="s">
-        <v>2106</v>
       </c>
       <c r="D1119" t="s">
         <v>11</v>
@@ -35848,7 +35845,7 @@
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="B1120" t="s">
         <v>813</v>
@@ -35874,7 +35871,7 @@
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="B1121" t="s">
         <v>389</v>
@@ -35900,10 +35897,10 @@
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B1122" t="s">
         <v>2109</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>2110</v>
       </c>
       <c r="C1122" t="s">
         <v>160</v>
@@ -35926,10 +35923,10 @@
     </row>
     <row r="1123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B1123" t="s">
         <v>2111</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>2112</v>
       </c>
       <c r="C1123" t="s">
         <v>389</v>
@@ -35952,10 +35949,10 @@
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1124" t="s">
         <v>2113</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>2114</v>
       </c>
       <c r="C1124" t="s">
         <v>1072</v>
@@ -35978,10 +35975,10 @@
     </row>
     <row r="1125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B1125" t="s">
         <v>2115</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>2116</v>
       </c>
       <c r="C1125" t="s">
         <v>247</v>
